--- a/docs/Nucleus_Enhancer_Validation_Results_v1.0.0.xlsx
+++ b/docs/Nucleus_Enhancer_Validation_Results_v1.0.0.xlsx
@@ -23,13 +23,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="777">
   <si>
     <t xml:space="preserve">How to use this workbook</t>
   </si>
   <si>
     <t xml:space="preserve">Work through the 'Test Cases' sheet top to bottom. For each row set the Result cell (dropdown: Pass / Fail / Partial / N/A / Not run), and record what you saw in 'Actual / notes', plus your initials and the date.
-There are 141 cases across all feature areas.
+There are 142 cases across all feature areas.
 This is an internal self-check, not a formal/Quality validation. Use the Diagnostics sheet (or docs/Nucleus_Enhancer_Diagnostics.md) to capture detail when something misbehaves.</t>
   </si>
   <si>
@@ -1422,6 +1422,18 @@
     <t xml:space="preserve">ME-04</t>
   </si>
   <si>
+    <t xml:space="preserve">Rename → version bump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change ONLY the Name; pick minor/major; give a reason; save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treated like a content change — version bumps, reason required, a new history snapshot is created. Status/team/date-only edits still don’t bump.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-05</t>
+  </si>
+  <si>
     <t xml:space="preserve">Clone as draft</t>
   </si>
   <si>
@@ -1431,7 +1443,7 @@
     <t xml:space="preserve">Opens new editor, status Draft, name '(Copy)', reason prefilled</t>
   </si>
   <si>
-    <t xml:space="preserve">ME-05</t>
+    <t xml:space="preserve">ME-06</t>
   </si>
   <si>
     <t xml:space="preserve">Delete with history</t>
@@ -1446,7 +1458,7 @@
     <t xml:space="preserve">Child versions removed first, then template; clear messaging</t>
   </si>
   <si>
-    <t xml:space="preserve">ME-06</t>
+    <t xml:space="preserve">ME-07</t>
   </si>
   <si>
     <t xml:space="preserve">Delete hidden without permission</t>
@@ -1461,7 +1473,7 @@
     <t xml:space="preserve">No Delete buttons appear (row or bulk) — gated on the real Salesforce permission, not just the IsAdmin flag; reload + sync after the permission change</t>
   </si>
   <si>
-    <t xml:space="preserve">ME-07</t>
+    <t xml:space="preserve">ME-08</t>
   </si>
   <si>
     <t xml:space="preserve">Status lifecycle</t>
@@ -2932,7 +2944,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K175"/>
+  <dimension ref="A1:K176"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.16"/>
@@ -6237,7 +6249,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
         <v>464</v>
       </c>
@@ -6286,168 +6298,168 @@
         <v>51</v>
       </c>
       <c r="E108" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="F108" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="F108" s="2" t="s">
+      <c r="G108" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="G108" s="2" t="s">
+      <c r="H108" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="H108" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K108" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="2" t="s">
-        <v>473</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>449</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E109" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F109" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="F109" s="2" t="s">
+      <c r="G109" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="G109" s="2" t="s">
+      <c r="H109" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="H109" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I109" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J109" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K109" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>449</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E110" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F110" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="F110" s="2" t="s">
+      <c r="G110" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="G110" s="2" t="s">
+      <c r="H110" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="H110" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I110" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J110" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K110" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="11" t="s">
+      <c r="B111" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="B111" s="11"/>
-      <c r="C111" s="11"/>
-      <c r="D111" s="11"/>
-      <c r="E111" s="11"/>
-      <c r="F111" s="11"/>
-      <c r="G111" s="11"/>
-      <c r="H111" s="11"/>
-      <c r="I111" s="11"/>
-      <c r="J111" s="11"/>
-      <c r="K111" s="11"/>
-    </row>
-    <row r="112" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="2" t="s">
+      <c r="D111" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="C112" s="2" t="s">
+      <c r="F111" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D112" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E112" s="2" t="s">
+      <c r="G111" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="F112" s="2" t="s">
+      <c r="H111" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="G112" s="2" t="s">
+      <c r="B112" s="11"/>
+      <c r="C112" s="11"/>
+      <c r="D112" s="11"/>
+      <c r="E112" s="11"/>
+      <c r="F112" s="11"/>
+      <c r="G112" s="11"/>
+      <c r="H112" s="11"/>
+      <c r="I112" s="11"/>
+      <c r="J112" s="11"/>
+      <c r="K112" s="11"/>
+    </row>
+    <row r="113" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="H112" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I112" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J112" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K112" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="2" t="s">
+      <c r="B113" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E113" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="F113" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="F113" s="2" t="s">
+      <c r="G113" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="H113" s="12" t="s">
         <v>43</v>
@@ -6464,19 +6476,19 @@
     </row>
     <row r="114" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>495</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>496</v>
@@ -6497,21 +6509,21 @@
         <v>43</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
         <v>498</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>499</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>500</v>
@@ -6532,21 +6544,21 @@
         <v>43</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
         <v>502</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>503</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>504</v>
@@ -6567,12 +6579,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
         <v>506</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>507</v>
@@ -6581,7 +6593,7 @@
         <v>51</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>508</v>
@@ -6602,21 +6614,21 @@
         <v>43</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>511</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>512</v>
@@ -6637,21 +6649,21 @@
         <v>43</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
         <v>514</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>515</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>516</v>
@@ -6677,22 +6689,22 @@
         <v>518</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>519</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E120" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="F120" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="F120" s="2" t="s">
+      <c r="G120" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="H120" s="12" t="s">
         <v>43</v>
@@ -6709,54 +6721,54 @@
     </row>
     <row r="121" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="C121" s="2" t="s">
+      <c r="D121" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E121" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="F121" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="H121" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K121" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D122" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E121" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="G121" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="H121" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I121" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J121" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K121" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="C122" s="2" t="s">
+      <c r="E122" s="2" t="s">
         <v>529</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>530</v>
@@ -6777,12 +6789,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
         <v>532</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>533</v>
@@ -6791,95 +6803,95 @@
         <v>39</v>
       </c>
       <c r="E123" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="F123" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="F123" s="2" t="s">
+      <c r="G123" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="G123" s="2" t="s">
+      <c r="H123" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="H123" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K123" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="11" t="s">
+      <c r="B124" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="B124" s="11"/>
-      <c r="C124" s="11"/>
-      <c r="D124" s="11"/>
-      <c r="E124" s="11"/>
-      <c r="F124" s="11"/>
-      <c r="G124" s="11"/>
-      <c r="H124" s="11"/>
-      <c r="I124" s="11"/>
-      <c r="J124" s="11"/>
-      <c r="K124" s="11"/>
-    </row>
-    <row r="125" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="2" t="s">
+      <c r="D124" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E124" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="C125" s="2" t="s">
+      <c r="F124" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="D125" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E125" s="2" t="s">
+      <c r="G124" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="F125" s="2" t="s">
+      <c r="H124" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="11" t="s">
         <v>541</v>
       </c>
-      <c r="G125" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="H125" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J125" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K125" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B125" s="11"/>
+      <c r="C125" s="11"/>
+      <c r="D125" s="11"/>
+      <c r="E125" s="11"/>
+      <c r="F125" s="11"/>
+      <c r="G125" s="11"/>
+      <c r="H125" s="11"/>
+      <c r="I125" s="11"/>
+      <c r="J125" s="11"/>
+      <c r="K125" s="11"/>
     </row>
     <row r="126" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E126" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="F126" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>541</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>546</v>
@@ -6902,7 +6914,7 @@
         <v>547</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>548</v>
@@ -6914,10 +6926,10 @@
         <v>549</v>
       </c>
       <c r="F127" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="G127" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="H127" s="12" t="s">
         <v>43</v>
@@ -6934,107 +6946,107 @@
     </row>
     <row r="128" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="C128" s="2" t="s">
+      <c r="D128" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="D128" s="2" t="s">
+      <c r="F128" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="H128" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D129" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E128" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="G128" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="H128" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K128" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="11" t="s">
-        <v>557</v>
-      </c>
-      <c r="B129" s="11"/>
-      <c r="C129" s="11"/>
-      <c r="D129" s="11"/>
-      <c r="E129" s="11"/>
-      <c r="F129" s="11"/>
-      <c r="G129" s="11"/>
-      <c r="H129" s="11"/>
-      <c r="I129" s="11"/>
-      <c r="J129" s="11"/>
-      <c r="K129" s="11"/>
-    </row>
-    <row r="130" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="2" t="s">
+      <c r="E129" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="C130" s="2" t="s">
+      <c r="F129" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="D130" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="F130" s="2" t="s">
+      <c r="G129" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="G130" s="2" t="s">
+      <c r="H129" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K129" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="11" t="s">
         <v>561</v>
       </c>
-      <c r="H130" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I130" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J130" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K130" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B130" s="11"/>
+      <c r="C130" s="11"/>
+      <c r="D130" s="11"/>
+      <c r="E130" s="11"/>
+      <c r="F130" s="11"/>
+      <c r="G130" s="11"/>
+      <c r="H130" s="11"/>
+      <c r="I130" s="11"/>
+      <c r="J130" s="11"/>
+      <c r="K130" s="11"/>
+    </row>
+    <row r="131" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
         <v>562</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>563</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E131" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F131" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>563</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>565</v>
@@ -7052,77 +7064,77 @@
         <v>43</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="11" t="s">
+    <row r="132" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B132" s="11"/>
-      <c r="C132" s="11"/>
-      <c r="D132" s="11"/>
-      <c r="E132" s="11"/>
-      <c r="F132" s="11"/>
-      <c r="G132" s="11"/>
-      <c r="H132" s="11"/>
-      <c r="I132" s="11"/>
-      <c r="J132" s="11"/>
-      <c r="K132" s="11"/>
-    </row>
-    <row r="133" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="2" t="s">
+      <c r="B132" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="C133" s="2" t="s">
+      <c r="D132" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="D133" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E133" s="2" t="s">
+      <c r="F132" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="G132" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="F133" s="2" t="s">
+      <c r="H132" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K132" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="11" t="s">
         <v>570</v>
       </c>
-      <c r="G133" s="2" t="s">
+      <c r="B133" s="11"/>
+      <c r="C133" s="11"/>
+      <c r="D133" s="11"/>
+      <c r="E133" s="11"/>
+      <c r="F133" s="11"/>
+      <c r="G133" s="11"/>
+      <c r="H133" s="11"/>
+      <c r="I133" s="11"/>
+      <c r="J133" s="11"/>
+      <c r="K133" s="11"/>
+    </row>
+    <row r="134" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="H133" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K133" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="2" t="s">
+      <c r="B134" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>572</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>573</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E134" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F134" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="F134" s="2" t="s">
+      <c r="G134" s="2" t="s">
         <v>575</v>
-      </c>
-      <c r="G134" s="2" t="s">
-        <v>576</v>
       </c>
       <c r="H134" s="12" t="s">
         <v>43</v>
@@ -7139,25 +7151,25 @@
     </row>
     <row r="135" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C135" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="C135" s="2" t="s">
+      <c r="D135" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E135" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="D135" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E135" s="2" t="s">
+      <c r="F135" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="F135" s="2" t="s">
+      <c r="G135" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="G135" s="2" t="s">
-        <v>581</v>
       </c>
       <c r="H135" s="12" t="s">
         <v>43</v>
@@ -7174,450 +7186,450 @@
     </row>
     <row r="136" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E136" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="F136" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="F136" s="2" t="s">
+      <c r="G136" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="G136" s="2" t="s">
+      <c r="H136" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K136" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="H136" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K136" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="88.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="2" t="s">
+      <c r="B137" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C137" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="C137" s="2" t="s">
+      <c r="D137" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E137" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="D137" s="2" t="s">
+      <c r="F137" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="H137" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K137" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="88.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="D138" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E137" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="H137" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I137" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J137" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K137" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="11" t="s">
-        <v>592</v>
-      </c>
-      <c r="B138" s="11"/>
-      <c r="C138" s="11"/>
-      <c r="D138" s="11"/>
-      <c r="E138" s="11"/>
-      <c r="F138" s="11"/>
-      <c r="G138" s="11"/>
-      <c r="H138" s="11"/>
-      <c r="I138" s="11"/>
-      <c r="J138" s="11"/>
-      <c r="K138" s="11"/>
-    </row>
-    <row r="139" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="2" t="s">
+      <c r="E138" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="C139" s="2" t="s">
+      <c r="F138" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="D139" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E139" s="2" t="s">
+      <c r="G138" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F139" s="2" t="s">
+      <c r="H138" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K138" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="11" t="s">
         <v>596</v>
       </c>
-      <c r="G139" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="H139" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I139" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J139" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K139" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B139" s="11"/>
+      <c r="C139" s="11"/>
+      <c r="D139" s="11"/>
+      <c r="E139" s="11"/>
+      <c r="F139" s="11"/>
+      <c r="G139" s="11"/>
+      <c r="H139" s="11"/>
+      <c r="I139" s="11"/>
+      <c r="J139" s="11"/>
+      <c r="K139" s="11"/>
     </row>
     <row r="140" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C140" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>599</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E140" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="F140" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="F140" s="2" t="s">
+      <c r="G140" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="G140" s="2" t="s">
+      <c r="H140" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K140" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="H140" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I140" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J140" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K140" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="11" t="s">
+      <c r="B141" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C141" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="B141" s="11"/>
-      <c r="C141" s="11"/>
-      <c r="D141" s="11"/>
-      <c r="E141" s="11"/>
-      <c r="F141" s="11"/>
-      <c r="G141" s="11"/>
-      <c r="H141" s="11"/>
-      <c r="I141" s="11"/>
-      <c r="J141" s="11"/>
-      <c r="K141" s="11"/>
-    </row>
-    <row r="142" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="2" t="s">
+      <c r="D141" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E141" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="C142" s="2" t="s">
+      <c r="F141" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="D142" s="2" t="s">
+      <c r="G141" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="H141" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K141" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="11" t="s">
+        <v>607</v>
+      </c>
+      <c r="B142" s="11"/>
+      <c r="C142" s="11"/>
+      <c r="D142" s="11"/>
+      <c r="E142" s="11"/>
+      <c r="F142" s="11"/>
+      <c r="G142" s="11"/>
+      <c r="H142" s="11"/>
+      <c r="I142" s="11"/>
+      <c r="J142" s="11"/>
+      <c r="K142" s="11"/>
+    </row>
+    <row r="143" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D143" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E142" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="G142" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="H142" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K142" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="11" t="s">
-        <v>609</v>
-      </c>
-      <c r="B143" s="11"/>
-      <c r="C143" s="11"/>
-      <c r="D143" s="11"/>
-      <c r="E143" s="11"/>
-      <c r="F143" s="11"/>
-      <c r="G143" s="11"/>
-      <c r="H143" s="11"/>
-      <c r="I143" s="11"/>
-      <c r="J143" s="11"/>
-      <c r="K143" s="11"/>
-    </row>
-    <row r="144" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="2" t="s">
+      <c r="E143" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="C144" s="2" t="s">
+      <c r="F143" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="D144" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E144" s="2" t="s">
+      <c r="G143" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="F144" s="2" t="s">
+      <c r="H143" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K143" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="11" t="s">
         <v>613</v>
       </c>
-      <c r="G144" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="H144" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K144" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B144" s="11"/>
+      <c r="C144" s="11"/>
+      <c r="D144" s="11"/>
+      <c r="E144" s="11"/>
+      <c r="F144" s="11"/>
+      <c r="G144" s="11"/>
+      <c r="H144" s="11"/>
+      <c r="I144" s="11"/>
+      <c r="J144" s="11"/>
+      <c r="K144" s="11"/>
     </row>
     <row r="145" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C145" s="2" t="s">
         <v>615</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>616</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E145" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F145" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="F145" s="2" t="s">
+      <c r="G145" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="G145" s="2" t="s">
+      <c r="H145" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K145" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="H145" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K145" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="11" t="s">
+      <c r="B146" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="B146" s="11"/>
-      <c r="C146" s="11"/>
-      <c r="D146" s="11"/>
-      <c r="E146" s="11"/>
-      <c r="F146" s="11"/>
-      <c r="G146" s="11"/>
-      <c r="H146" s="11"/>
-      <c r="I146" s="11"/>
-      <c r="J146" s="11"/>
-      <c r="K146" s="11"/>
-    </row>
-    <row r="147" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="2" t="s">
+      <c r="D146" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E146" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="C147" s="2" t="s">
+      <c r="F146" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="D147" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F147" s="2" t="s">
+      <c r="G146" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="G147" s="2" t="s">
+      <c r="H146" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K146" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="H147" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K147" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B147" s="11"/>
+      <c r="C147" s="11"/>
+      <c r="D147" s="11"/>
+      <c r="E147" s="11"/>
+      <c r="F147" s="11"/>
+      <c r="G147" s="11"/>
+      <c r="H147" s="11"/>
+      <c r="I147" s="11"/>
+      <c r="J147" s="11"/>
+      <c r="K147" s="11"/>
+    </row>
+    <row r="148" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
         <v>625</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>626</v>
       </c>
       <c r="D148" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="H148" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K148" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="D149" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E148" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="G148" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="H148" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K148" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="11" t="s">
-        <v>630</v>
-      </c>
-      <c r="B149" s="11"/>
-      <c r="C149" s="11"/>
-      <c r="D149" s="11"/>
-      <c r="E149" s="11"/>
-      <c r="F149" s="11"/>
-      <c r="G149" s="11"/>
-      <c r="H149" s="11"/>
-      <c r="I149" s="11"/>
-      <c r="J149" s="11"/>
-      <c r="K149" s="11"/>
-    </row>
-    <row r="150" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="2" t="s">
+      <c r="E149" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="C150" s="2" t="s">
+      <c r="F149" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="D150" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E150" s="2" t="s">
+      <c r="G149" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="F150" s="2" t="s">
+      <c r="H149" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K149" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="11" t="s">
         <v>634</v>
       </c>
-      <c r="G150" s="2" t="s">
+      <c r="B150" s="11"/>
+      <c r="C150" s="11"/>
+      <c r="D150" s="11"/>
+      <c r="E150" s="11"/>
+      <c r="F150" s="11"/>
+      <c r="G150" s="11"/>
+      <c r="H150" s="11"/>
+      <c r="I150" s="11"/>
+      <c r="J150" s="11"/>
+      <c r="K150" s="11"/>
+    </row>
+    <row r="151" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="H150" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I150" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J150" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K150" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="2" t="s">
+      <c r="B151" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>636</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>637</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E151" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="F151" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="F151" s="2" t="s">
+      <c r="G151" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>640</v>
       </c>
       <c r="H151" s="12" t="s">
         <v>43</v>
@@ -7634,215 +7646,215 @@
     </row>
     <row r="152" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="B152" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="C152" s="2" t="s">
+      <c r="D152" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E152" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="D152" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E152" s="2" t="s">
+      <c r="F152" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="F152" s="2" t="s">
+      <c r="G152" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="G152" s="2" t="s">
+      <c r="H152" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="H152" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I152" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J152" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K152" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="2" t="s">
+      <c r="B153" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>647</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E153" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="F153" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="F153" s="2" t="s">
+      <c r="G153" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="G153" s="2" t="s">
+      <c r="H153" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K153" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="H153" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K153" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="2" t="s">
+      <c r="B154" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>651</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>652</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E154" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F154" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="F154" s="2" t="s">
+      <c r="G154" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="G154" s="2" t="s">
+      <c r="H154" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="H154" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I154" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J154" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K154" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="2" t="s">
+      <c r="B155" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="C155" s="2" t="s">
+      <c r="D155" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E155" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="D155" s="2" t="s">
+      <c r="F155" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="H155" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K155" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="D156" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E155" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="H155" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I155" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J155" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K155" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="11" t="s">
-        <v>661</v>
-      </c>
-      <c r="B156" s="11"/>
-      <c r="C156" s="11"/>
-      <c r="D156" s="11"/>
-      <c r="E156" s="11"/>
-      <c r="F156" s="11"/>
-      <c r="G156" s="11"/>
-      <c r="H156" s="11"/>
-      <c r="I156" s="11"/>
-      <c r="J156" s="11"/>
-      <c r="K156" s="11"/>
-    </row>
-    <row r="157" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="2" t="s">
+      <c r="E156" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="C157" s="2" t="s">
+      <c r="F156" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="D157" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E157" s="2" t="s">
+      <c r="G156" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="F157" s="2" t="s">
+      <c r="H156" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="11" t="s">
         <v>665</v>
       </c>
-      <c r="G157" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="H157" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I157" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J157" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K157" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B157" s="11"/>
+      <c r="C157" s="11"/>
+      <c r="D157" s="11"/>
+      <c r="E157" s="11"/>
+      <c r="F157" s="11"/>
+      <c r="G157" s="11"/>
+      <c r="H157" s="11"/>
+      <c r="I157" s="11"/>
+      <c r="J157" s="11"/>
+      <c r="K157" s="11"/>
     </row>
     <row r="158" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>667</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>668</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E158" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="F158" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="F158" s="2" t="s">
+      <c r="G158" s="2" t="s">
         <v>670</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>671</v>
       </c>
       <c r="H158" s="12" t="s">
         <v>43</v>
@@ -7859,314 +7871,314 @@
     </row>
     <row r="159" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>673</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E159" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="F159" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="F159" s="2" t="s">
+      <c r="G159" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="G159" s="2" t="s">
+      <c r="H159" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K159" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="H159" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I159" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J159" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K159" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="2" t="s">
+      <c r="B160" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>678</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E160" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="F160" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="F160" s="2" t="s">
+      <c r="G160" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="G160" s="2" t="s">
+      <c r="H160" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K160" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="H160" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I160" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J160" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K160" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="2" t="s">
+      <c r="B161" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="C161" s="2" t="s">
+      <c r="D161" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E161" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="D161" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E161" s="2" t="s">
+      <c r="F161" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="F161" s="2" t="s">
+      <c r="G161" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="G161" s="2" t="s">
+      <c r="H161" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I161" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K161" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="H161" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I161" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J161" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K161" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="2" t="s">
+      <c r="B162" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>688</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E162" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="F162" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="F162" s="2" t="s">
+      <c r="G162" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="G162" s="2" t="s">
+      <c r="H162" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I162" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J162" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K162" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="H162" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I162" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J162" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K162" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="11" t="s">
+      <c r="B163" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="C163" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="B163" s="11"/>
-      <c r="C163" s="11"/>
-      <c r="D163" s="11"/>
-      <c r="E163" s="11"/>
-      <c r="F163" s="11"/>
-      <c r="G163" s="11"/>
-      <c r="H163" s="11"/>
-      <c r="I163" s="11"/>
-      <c r="J163" s="11"/>
-      <c r="K163" s="11"/>
-    </row>
-    <row r="164" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="2" t="s">
+      <c r="D163" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E163" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="C164" s="2" t="s">
+      <c r="F163" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="D164" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E164" s="2" t="s">
+      <c r="G163" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="F164" s="2" t="s">
+      <c r="H163" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I163" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J163" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K163" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="11" t="s">
         <v>696</v>
       </c>
-      <c r="G164" s="2" t="s">
+      <c r="B164" s="11"/>
+      <c r="C164" s="11"/>
+      <c r="D164" s="11"/>
+      <c r="E164" s="11"/>
+      <c r="F164" s="11"/>
+      <c r="G164" s="11"/>
+      <c r="H164" s="11"/>
+      <c r="I164" s="11"/>
+      <c r="J164" s="11"/>
+      <c r="K164" s="11"/>
+    </row>
+    <row r="165" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="H164" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I164" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J164" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K164" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="165" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="2" t="s">
+      <c r="B165" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="C165" s="2" t="s">
         <v>698</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>699</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E165" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="F165" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="F165" s="2" t="s">
+      <c r="G165" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="G165" s="2" t="s">
+      <c r="H165" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I165" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J165" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="H165" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I165" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J165" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K165" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="166" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="2" t="s">
+      <c r="B166" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="C166" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="C166" s="2" t="s">
+      <c r="D166" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E166" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="D166" s="2" t="s">
+      <c r="F166" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="H166" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J166" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K166" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="D167" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E166" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="F166" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="G166" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="H166" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I166" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J166" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K166" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="167" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="C167" s="2" t="s">
+      <c r="E167" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="D167" s="2" t="s">
+      <c r="F167" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="H167" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I167" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J167" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K167" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="D168" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E167" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="G167" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="H167" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I167" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J167" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K167" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="C168" s="2" t="s">
+      <c r="E168" s="2" t="s">
         <v>714</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>710</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>715</v>
@@ -8192,7 +8204,7 @@
         <v>717</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>718</v>
@@ -8201,133 +8213,133 @@
         <v>57</v>
       </c>
       <c r="E169" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="F169" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="F169" s="2" t="s">
+      <c r="G169" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="G169" s="2" t="s">
+      <c r="H169" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I169" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J169" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K169" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="H169" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I169" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J169" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K169" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="170" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="11" t="s">
+      <c r="B170" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="C170" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="B170" s="11"/>
-      <c r="C170" s="11"/>
-      <c r="D170" s="11"/>
-      <c r="E170" s="11"/>
-      <c r="F170" s="11"/>
-      <c r="G170" s="11"/>
-      <c r="H170" s="11"/>
-      <c r="I170" s="11"/>
-      <c r="J170" s="11"/>
-      <c r="K170" s="11"/>
-    </row>
-    <row r="171" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="2" t="s">
+      <c r="D170" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E170" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="B171" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="C171" s="2" t="s">
+      <c r="F170" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="D171" s="2" t="s">
+      <c r="G170" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="H170" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J170" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K170" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="11" t="s">
+        <v>726</v>
+      </c>
+      <c r="B171" s="11"/>
+      <c r="C171" s="11"/>
+      <c r="D171" s="11"/>
+      <c r="E171" s="11"/>
+      <c r="F171" s="11"/>
+      <c r="G171" s="11"/>
+      <c r="H171" s="11"/>
+      <c r="I171" s="11"/>
+      <c r="J171" s="11"/>
+      <c r="K171" s="11"/>
+    </row>
+    <row r="172" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="D172" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E171" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="F171" s="2" t="s">
+      <c r="E172" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="H172" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I172" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J172" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K172" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B173" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="G171" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="H171" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I171" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J171" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K171" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="D172" s="2" t="s">
+      <c r="C173" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="D173" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E172" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="F172" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="G172" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="H172" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I172" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J172" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K172" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="173" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="C173" s="2" t="s">
+      <c r="E173" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="D173" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E173" s="2" t="s">
+      <c r="F173" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="F173" s="2" t="s">
+      <c r="G173" s="2" t="s">
         <v>736</v>
-      </c>
-      <c r="G173" s="2" t="s">
-        <v>737</v>
       </c>
       <c r="H173" s="12" t="s">
         <v>43</v>
@@ -8344,71 +8356,106 @@
     </row>
     <row r="174" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="C174" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="B174" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="C174" s="2" t="s">
+      <c r="D174" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E174" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="D174" s="2" t="s">
+      <c r="F174" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="H174" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I174" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J174" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K174" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="D175" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E174" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="F174" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="G174" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="H174" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I174" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J174" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K174" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="175" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="C175" s="2" t="s">
+      <c r="E175" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="D175" s="2" t="s">
+      <c r="F175" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="H175" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I175" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J175" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K175" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="D176" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E175" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="F175" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="G175" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="H175" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I175" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J175" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K175" s="2" t="s">
+      <c r="E176" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="H176" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I176" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J176" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K176" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -8435,18 +8482,18 @@
     <mergeCell ref="A91:K91"/>
     <mergeCell ref="A96:K96"/>
     <mergeCell ref="A103:K103"/>
-    <mergeCell ref="A111:K111"/>
-    <mergeCell ref="A124:K124"/>
-    <mergeCell ref="A129:K129"/>
-    <mergeCell ref="A132:K132"/>
-    <mergeCell ref="A138:K138"/>
-    <mergeCell ref="A141:K141"/>
-    <mergeCell ref="A143:K143"/>
-    <mergeCell ref="A146:K146"/>
-    <mergeCell ref="A149:K149"/>
-    <mergeCell ref="A156:K156"/>
-    <mergeCell ref="A163:K163"/>
-    <mergeCell ref="A170:K170"/>
+    <mergeCell ref="A112:K112"/>
+    <mergeCell ref="A125:K125"/>
+    <mergeCell ref="A130:K130"/>
+    <mergeCell ref="A133:K133"/>
+    <mergeCell ref="A139:K139"/>
+    <mergeCell ref="A142:K142"/>
+    <mergeCell ref="A144:K144"/>
+    <mergeCell ref="A147:K147"/>
+    <mergeCell ref="A150:K150"/>
+    <mergeCell ref="A157:K157"/>
+    <mergeCell ref="A164:K164"/>
+    <mergeCell ref="A171:K171"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:H400">
     <cfRule type="cellIs" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -8463,7 +8510,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Choose Pass / Fail / Partial / N/A / Not run" promptTitle="Result" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H7 H9:H13 H15:H20 H22:H26 H28:H30 H32 H34:H35 H37:H40 H42:H44 H46:H55 H57:H61 H63:H69 H71:H75 H77 H79:H82 H84:H87 H89:H90 H92:H95 H97:H102 H104:H110 H112:H123 H125:H128 H130:H131 H133:H137 H139:H140 H142 H144:H145 H147:H148 H150:H155 H157:H162 H164:H169 H171:H175" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Choose Pass / Fail / Partial / N/A / Not run" promptTitle="Result" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H7 H9:H13 H15:H20 H22:H26 H28:H30 H32 H34:H35 H37:H40 H42:H44 H46:H55 H57:H61 H63:H69 H71:H75 H77 H79:H82 H84:H87 H89:H90 H92:H95 H97:H102 H104:H111 H113:H124 H126:H129 H131:H132 H134:H138 H140:H141 H143 H145:H146 H148:H149 H151:H156 H158:H163 H165:H170 H172:H176" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8492,13 +8539,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B2" s="3"/>
     </row>
@@ -8549,7 +8596,7 @@
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B8" s="2" t="e">
         <f aca="false">of:=COUNTA('Test Cases'!A3:A400)-COUNTIF('Test Cases'!D3:D400,"")</f>
@@ -8558,7 +8605,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B9" s="3"/>
     </row>
@@ -8744,7 +8791,7 @@
     </row>
     <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B30" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"RTE editor",'Test Cases'!H3:H400,"Pass")</f>
@@ -8753,7 +8800,7 @@
     </row>
     <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B31" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Teams",'Test Cases'!H3:H400,"Pass")</f>
@@ -8762,7 +8809,7 @@
     </row>
     <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B32" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"History",'Test Cases'!H3:H400,"Pass")</f>
@@ -8771,7 +8818,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B33" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Usage",'Test Cases'!H3:H400,"Pass")</f>
@@ -8780,7 +8827,7 @@
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B34" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Read-only",'Test Cases'!H3:H400,"Pass")</f>
@@ -8789,7 +8836,7 @@
     </row>
     <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B35" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Dark mode",'Test Cases'!H3:H400,"Pass")</f>
@@ -8798,7 +8845,7 @@
     </row>
     <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B36" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Background",'Test Cases'!H3:H400,"Pass")</f>
@@ -8807,7 +8854,7 @@
     </row>
     <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B37" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Diagnostics",'Test Cases'!H3:H400,"Pass")</f>
@@ -8816,7 +8863,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B38" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Security",'Test Cases'!H3:H400,"Pass")</f>
@@ -8825,7 +8872,7 @@
     </row>
     <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B39" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Acknowledgements",'Test Cases'!H3:H400,"Pass")</f>
@@ -8834,7 +8881,7 @@
     </row>
     <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B40" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Suggestions",'Test Cases'!H3:H400,"Pass")</f>
@@ -8843,7 +8890,7 @@
     </row>
     <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="B41" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"UX",'Test Cases'!H3:H400,"Pass")</f>
@@ -8880,88 +8927,88 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
     </row>
   </sheetData>
